--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487971_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487971_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.804</v>
+        <v>5.9817</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3426</v>
+        <v>4.773</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4614</v>
+        <v>1.2087</v>
       </c>
       <c r="G2" t="n">
         <v>4.6121</v>
@@ -610,13 +610,13 @@
         <v>1.5858</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3307</v>
+        <v>0.5084</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3816</v>
+        <v>0.0488</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7123</v>
+        <v>0.4596</v>
       </c>
       <c r="V2" t="n">
         <v>0.2666</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.922</v>
+        <v>3.6592</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1218</v>
+        <v>0.494</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8002</v>
+        <v>3.1652</v>
       </c>
       <c r="G3" t="n">
         <v>0.948</v>
@@ -688,13 +688,13 @@
         <v>2.3787</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6568</v>
+        <v>1.394</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0942</v>
+        <v>0.4664</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5626</v>
+        <v>0.9276</v>
       </c>
       <c r="V3" t="n">
         <v>-0.0704</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5194</v>
+        <v>2.4134</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.2956</v>
+        <v>-1.4577</v>
       </c>
       <c r="F4" t="n">
-        <v>3.8149</v>
+        <v>3.8711</v>
       </c>
       <c r="G4" t="n">
         <v>3.2605</v>
@@ -766,13 +766,13 @@
         <v>2.5769</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7151</v>
+        <v>0.1789</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.4975</v>
+        <v>-0.6597</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7824</v>
+        <v>0.8386</v>
       </c>
       <c r="V4" t="n">
         <v>2.3438</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4468</v>
+        <v>1.2285</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5566</v>
+        <v>1.619</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1097</v>
+        <v>-0.3905</v>
       </c>
       <c r="G5" t="n">
         <v>1.782</v>
@@ -844,13 +844,13 @@
         <v>1.3876</v>
       </c>
       <c r="S5" t="n">
-        <v>0.958</v>
+        <v>0.7396</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3192</v>
+        <v>-0.2568</v>
       </c>
       <c r="U5" t="n">
-        <v>1.2772</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>-2.6808</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0065</v>
+        <v>1.2021</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0375</v>
+        <v>-0.1039</v>
       </c>
       <c r="F6" t="n">
-        <v>0.969</v>
+        <v>1.306</v>
       </c>
       <c r="G6" t="n">
         <v>0.0013</v>
@@ -922,13 +922,13 @@
         <v>0.7929</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0543</v>
+        <v>0.1413</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0696</v>
+        <v>-0.211</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0154</v>
+        <v>0.3523</v>
       </c>
       <c r="V6" t="n">
         <v>0.2666</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. CORTES ANDRADES</t>
+          <t>D. TERRÓN FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8149</v>
+        <v>0.3027</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2598</v>
+        <v>0.3027</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0747</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.1344</v>
+        <v>0.3027</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1624</v>
+        <v>0.3027</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.972</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.02</v>
+        <v>0.3027</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1003</v>
+        <v>0.3027</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0804</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1144</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.062</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0524</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1893</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4845</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4847</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9998</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. WOLKOWYSKI</t>
+          <t>D. CORTES ANDRADES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3803</v>
+        <v>0.1995</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.1937</v>
+        <v>-0.7068</v>
       </c>
       <c r="F8" t="n">
-        <v>3.5741</v>
+        <v>0.9062</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2191</v>
+        <v>-1.1344</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.2062</v>
+        <v>-0.1624</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9871</v>
+        <v>-0.972</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.197</v>
+        <v>-0.02</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.3577</v>
+        <v>-0.1003</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1607</v>
+        <v>0.0804</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9779</v>
+        <v>-1.1144</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1515</v>
+        <v>-0.062</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8264</v>
+        <v>-1.0524</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1893</v>
+        <v>0.1982</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9733</v>
+        <v>-0.9911</v>
       </c>
       <c r="R8" t="n">
-        <v>1.784</v>
+        <v>1.1893</v>
       </c>
       <c r="S8" t="n">
-        <v>1.7888</v>
+        <v>0.8691</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9766</v>
+        <v>0.0377</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8122</v>
+        <v>0.8313</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. TERRÓN FERNÁNDEZ</t>
+          <t>E. LOPEZ GARCIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3027</v>
+        <v>-0.0853</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3027</v>
+        <v>-0.8615</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.7763</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3027</v>
+        <v>-0.2473</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3027</v>
+        <v>1.3101</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-1.5573</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3027</v>
+        <v>0.0579</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3027</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.6351</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-0.3052</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>0.6171</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0.9223</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.7929</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.6268</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.0717</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.5551</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. LOPEZ GARCIA</t>
+          <t>T. WOLKOWYSKI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4356</v>
+        <v>-0.5688</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1277</v>
+        <v>-3.9463</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6919999999999999</v>
+        <v>3.3775</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2473</v>
+        <v>-0.2191</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3101</v>
+        <v>-1.2062</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5573</v>
+        <v>0.9871</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0579</v>
+        <v>-1.197</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6929999999999999</v>
+        <v>-1.3577</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6351</v>
+        <v>0.1607</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3052</v>
+        <v>0.9779</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6171</v>
+        <v>0.1515</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9223</v>
+        <v>0.8264</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1982</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9911</v>
+        <v>-2.9733</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7929</v>
+        <v>1.784</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2764</v>
+        <v>0.8397</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1944</v>
+        <v>0.2241</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4709</v>
+        <v>0.6156</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.0751</v>
+        <v>-0.8746</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.8381</v>
+        <v>-3.3287</v>
       </c>
       <c r="F11" t="n">
-        <v>2.763</v>
+        <v>2.4541</v>
       </c>
       <c r="G11" t="n">
         <v>1.0641</v>
@@ -1312,13 +1312,13 @@
         <v>1.3876</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0004</v>
+        <v>0.2</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8736</v>
+        <v>-0.3642</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8731</v>
+        <v>0.5642</v>
       </c>
       <c r="V11" t="n">
         <v>-1.5441</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9033</v>
+        <v>-1.6027</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8214</v>
+        <v>-1.7174</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0819</v>
+        <v>0.1147</v>
       </c>
       <c r="G12" t="n">
         <v>-1.4367</v>
@@ -1390,13 +1390,13 @@
         <v>2.1805</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7243000000000001</v>
+        <v>0.5763</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.5599</v>
+        <v>-0.4559</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8357</v>
+        <v>1.0322</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9405</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.3572</v>
+        <v>-7.4943</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.5764</v>
+        <v>-5.882</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.7808</v>
+        <v>-1.6123</v>
       </c>
       <c r="G13" t="n">
         <v>-2.8425</v>
@@ -1468,13 +1468,13 @@
         <v>0.7929</v>
       </c>
       <c r="S13" t="n">
-        <v>0.009599999999999999</v>
+        <v>-0.1276</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0072</v>
+        <v>-0.3128</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0168</v>
+        <v>0.1853</v>
       </c>
       <c r="V13" t="n">
         <v>-2.3438</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.425400000000004</v>
+        <v>4.361400000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-11.7515</v>
+        <v>-10.8156</v>
       </c>
       <c r="F14" t="n">
-        <v>15.1769</v>
+        <v>15.177</v>
       </c>
       <c r="G14" t="n">
         <v>6.090700000000002</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9589</v>
+        <v>1.958899999999999</v>
       </c>
       <c r="I14" t="n">
         <v>4.131900000000001</v>
@@ -1534,7 +1534,7 @@
         <v>1.1462</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3940000000000001</v>
+        <v>-0.394</v>
       </c>
       <c r="P14" t="n">
         <v>-2.9733</v>
@@ -1546,13 +1546,13 @@
         <v>16.8491</v>
       </c>
       <c r="S14" t="n">
-        <v>5.010699999999999</v>
+        <v>5.946499999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.3475</v>
+        <v>-1.4117</v>
       </c>
       <c r="U14" t="n">
-        <v>7.3584</v>
+        <v>7.3583</v>
       </c>
       <c r="V14" t="n">
         <v>-4.7026</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.1092</v>
+        <v>4.6081</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8771</v>
+        <v>2.4883</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2321</v>
+        <v>2.1198</v>
       </c>
       <c r="G15" t="n">
         <v>1.1528</v>
@@ -1624,13 +1624,13 @@
         <v>3.568</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.7158</v>
+        <v>-1.2169</v>
       </c>
       <c r="T15" t="n">
-        <v>-2.2463</v>
+        <v>-1.6351</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5305</v>
+        <v>0.4182</v>
       </c>
       <c r="V15" t="n">
         <v>2.2935</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.4173</v>
+        <v>3.5609</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8545</v>
+        <v>1.5489</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5627</v>
+        <v>2.012</v>
       </c>
       <c r="G16" t="n">
         <v>0.5582</v>
@@ -1702,13 +1702,13 @@
         <v>3.3698</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1063</v>
+        <v>-0.9627</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7632</v>
+        <v>-1.0689</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3431</v>
+        <v>0.1062</v>
       </c>
       <c r="V16" t="n">
         <v>3.7672</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5622</v>
+        <v>0.6223</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.4728</v>
+        <v>-1.9635</v>
       </c>
       <c r="F17" t="n">
-        <v>3.035</v>
+        <v>2.5857</v>
       </c>
       <c r="G17" t="n">
         <v>-2.052</v>
@@ -1780,13 +1780,13 @@
         <v>3.568</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0669</v>
+        <v>-1.0068</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.9967</v>
+        <v>-1.4874</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9298</v>
+        <v>0.4806</v>
       </c>
       <c r="V17" t="n">
         <v>2.2935</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O. GARCIA JIMENEZ</t>
+          <t>F. GARCIA GARRIDO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,19 +1813,19 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1036</v>
+        <v>0.0236</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5543</v>
+        <v>-0.2101</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4508</v>
+        <v>0.2337</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4695</v>
+        <v>0.0078</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4695</v>
+        <v>0.0078</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1840,40 +1840,40 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4695</v>
+        <v>0.0078</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4695</v>
+        <v>0.0078</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5731000000000001</v>
+        <v>-0.5194</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5543</v>
+        <v>-0.2101</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0187</v>
+        <v>-0.3093</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.337</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1132</v>
+        <v>-0.0851</v>
       </c>
       <c r="E19" t="n">
         <v>-0.0624</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0508</v>
+        <v>-0.0227</v>
       </c>
       <c r="G19" t="n">
         <v>-0.2677</v>
@@ -1936,13 +1936,13 @@
         <v>0.1982</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0437</v>
+        <v>-0.0156</v>
       </c>
       <c r="T19" t="n">
         <v>-0.0624</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0187</v>
+        <v>0.0468</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. GARCIA GARRIDO</t>
+          <t>O. GARCIA JIMENEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,19 +1969,19 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2186</v>
+        <v>-0.2758</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.312</v>
+        <v>0.1469</v>
       </c>
       <c r="F20" t="n">
-        <v>0.09329999999999999</v>
+        <v>-0.4227</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0078</v>
+        <v>-0.4695</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0078</v>
+        <v>-0.4695</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -1996,40 +1996,40 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0078</v>
+        <v>-0.4695</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0078</v>
+        <v>-0.4695</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7617</v>
+        <v>0.1937</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.312</v>
+        <v>0.1469</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4497</v>
+        <v>0.0468</v>
       </c>
       <c r="V20" t="n">
-        <v>0.337</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.337</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.528</v>
+        <v>-0.5633</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7769</v>
+        <v>-1.9806</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2489</v>
+        <v>1.4174</v>
       </c>
       <c r="G21" t="n">
         <v>-1.6756</v>
@@ -2092,13 +2092,13 @@
         <v>0.9911</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1564</v>
+        <v>0.1212</v>
       </c>
       <c r="T21" t="n">
-        <v>0.18</v>
+        <v>-0.0238</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0235</v>
+        <v>0.145</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6815</v>
+        <v>-1.5235</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8245</v>
+        <v>-1.7227</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1431</v>
+        <v>0.1992</v>
       </c>
       <c r="G22" t="n">
         <v>-0.1213</v>
@@ -2170,13 +2170,13 @@
         <v>0.9911</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6196</v>
+        <v>-0.4616</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5616</v>
+        <v>-0.4597</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0581</v>
+        <v>-0.0019</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9405</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8686</v>
+        <v>-2.9885</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.3487</v>
+        <v>-5.6543</v>
       </c>
       <c r="F23" t="n">
-        <v>3.4801</v>
+        <v>2.6658</v>
       </c>
       <c r="G23" t="n">
         <v>-1.0217</v>
@@ -2248,13 +2248,13 @@
         <v>2.9733</v>
       </c>
       <c r="S23" t="n">
-        <v>1.1419</v>
+        <v>0.022</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.888</v>
+        <v>-1.1936</v>
       </c>
       <c r="U23" t="n">
-        <v>2.0299</v>
+        <v>1.2156</v>
       </c>
       <c r="V23" t="n">
         <v>-1.7906</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.4624</v>
+        <v>-3.1287</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.6491</v>
+        <v>-3.3435</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1867</v>
+        <v>0.2148</v>
       </c>
       <c r="G24" t="n">
         <v>-0.9886</v>
@@ -2326,13 +2326,13 @@
         <v>0.9911</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4915</v>
+        <v>-0.1578</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6864</v>
+        <v>-0.3808</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1949</v>
+        <v>0.223</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.7453</v>
+        <v>-3.6755</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.0165</v>
+        <v>-4.4239</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2711</v>
+        <v>0.7485000000000001</v>
       </c>
       <c r="G25" t="n">
         <v>-1.2131</v>
@@ -2404,13 +2404,13 @@
         <v>2.9733</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.0766</v>
+        <v>-1.0067</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5760999999999999</v>
+        <v>-0.9835</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5004999999999999</v>
+        <v>-0.0232</v>
       </c>
       <c r="V25" t="n">
         <v>-1.2574</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.425299999999998</v>
+        <v>-3.4255</v>
       </c>
       <c r="E26" t="n">
-        <v>-15.177</v>
+        <v>-15.1769</v>
       </c>
       <c r="F26" t="n">
-        <v>11.7514</v>
+        <v>11.7515</v>
       </c>
       <c r="G26" t="n">
         <v>-6.0907</v>
@@ -2482,16 +2482,16 @@
         <v>19.8221</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.0107</v>
+        <v>-5.0106</v>
       </c>
       <c r="T26" t="n">
         <v>-7.3584</v>
       </c>
       <c r="U26" t="n">
-        <v>2.3476</v>
+        <v>2.347799999999999</v>
       </c>
       <c r="V26" t="n">
-        <v>4.702699999999998</v>
+        <v>4.7027</v>
       </c>
       <c r="W26" t="n">
         <v>9.7827</v>
